--- a/survey_templates/033_telecommuting_productivity_impact_survey--survey_templates.xlsx
+++ b/survey_templates/033_telecommuting_productivity_impact_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -860,29 +860,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>slightly_decreased_productivity</t>
+          <t>much_decreased_productivity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slightly Decreased Productivity</t>
+          <t>Much Decreased Productivity</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>productivity_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>much_decreased_productivity</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Much Decreased Productivity</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -945,29 +945,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>frequency_worked_from_home_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1030,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>frequency_worked_from_home_choices</t>
+          <t>work_arrangements_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>full_time_remote</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Full Time Remote</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>full_time_remote</t>
+          <t>part_time_remote</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Full Time Remote</t>
+          <t>Part Time Remote</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>part_time_remote</t>
+          <t>hybrid_remote</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Part Time Remote</t>
+          <t>Hybrid Remote</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hybrid_remote</t>
+          <t>in_office</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hybrid Remote</t>
+          <t>In Office</t>
         </is>
       </c>
     </row>
@@ -1115,29 +1115,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>in_office</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>In Office</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>work_arrangements_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1200,29 +1200,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>collaboration_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1285,27 +1285,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>collaboration_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Never</t>
         </is>
